--- a/data/Prices/Prices_data.xlsx
+++ b/data/Prices/Prices_data.xlsx
@@ -1,27 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/Prices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:9_{F62047AF-F3A2-4C22-8968-B3120DE95FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{464E0054-FE51-466B-AE69-AC9A62D3FCD9}"/>
+  <xr:revisionPtr revIDLastSave="458" documentId="13_ncr:9_{F62047AF-F3A2-4C22-8968-B3120DE95FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F97160AD-C6FC-4667-9F7F-97D34292217A}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EC527E92-74B5-47BF-A0A5-1376B6EBFE76}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{EC527E92-74B5-47BF-A0A5-1376B6EBFE76}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="2" r:id="rId1"/>
     <sheet name="data" sheetId="5" r:id="rId2"/>
     <sheet name="Can_export_2013_2023" sheetId="4" r:id="rId3"/>
     <sheet name="Lai2025_SI2" sheetId="3" r:id="rId4"/>
+    <sheet name="MAC" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Can_export_2013_2023!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Lai2025_SI2!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">MAC!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="158">
   <si>
     <t>Commodity</t>
   </si>
@@ -461,12 +463,69 @@
   </si>
   <si>
     <t>Ag</t>
+  </si>
+  <si>
+    <t>Province</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>$000</t>
+  </si>
+  <si>
+    <t>QC</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>MB</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>Nunavut</t>
+  </si>
+  <si>
+    <t>$/kg</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Iron ore</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>kt</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>Newfoundland</t>
+  </si>
+  <si>
+    <t>PGMs</t>
+  </si>
+  <si>
+    <t>MAC - The Mining Story 2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -950,12 +1009,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1361,9 +1422,9 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
     <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2761,7 +2822,7 @@
     <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -2843,7 +2904,7 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>9.3391084359322267</v>
+        <v>9.3391084359322303</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
@@ -3169,4 +3230,574 @@
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{740C5C6D-65F6-485E-9AA5-45CED2729404}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.81640625" customWidth="1"/>
+    <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2">
+        <v>50808</v>
+      </c>
+      <c r="E2">
+        <v>4112214</v>
+      </c>
+      <c r="F2" s="5">
+        <f t="shared" ref="F2:F7" si="0">(E2*1000)/D2</f>
+        <v>80936.348606518659</v>
+      </c>
+      <c r="G2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3">
+        <v>88557</v>
+      </c>
+      <c r="E3">
+        <v>6495628</v>
+      </c>
+      <c r="F3" s="5">
+        <f t="shared" si="0"/>
+        <v>73349.684384069013</v>
+      </c>
+      <c r="G3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4">
+        <v>4085</v>
+      </c>
+      <c r="E4">
+        <v>308262</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>75461.933904528763</v>
+      </c>
+      <c r="G4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5">
+        <v>18476</v>
+      </c>
+      <c r="E5">
+        <v>1525896</v>
+      </c>
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>82588.00606191816</v>
+      </c>
+      <c r="G5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6">
+        <v>25199</v>
+      </c>
+      <c r="E6">
+        <v>1928389</v>
+      </c>
+      <c r="F6" s="5">
+        <f t="shared" si="0"/>
+        <v>76526.409778165806</v>
+      </c>
+      <c r="G6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7">
+        <v>198567</v>
+      </c>
+      <c r="E7">
+        <v>15143920</v>
+      </c>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>76266.046221174722</v>
+      </c>
+      <c r="G7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8">
+        <v>48043</v>
+      </c>
+      <c r="E8">
+        <v>6053875</v>
+      </c>
+      <c r="F8" s="5">
+        <f>(E8*1000)/(D8*1000000)</f>
+        <v>0.12600951231188726</v>
+      </c>
+      <c r="G8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9">
+        <v>17876</v>
+      </c>
+      <c r="E9">
+        <v>130404</v>
+      </c>
+      <c r="F9" s="5">
+        <f>(E9*1000)/(D9*1000)</f>
+        <v>7.2949205638845376</v>
+      </c>
+      <c r="G9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10">
+        <v>221803</v>
+      </c>
+      <c r="E10">
+        <v>2226060</v>
+      </c>
+      <c r="F10" s="5">
+        <f t="shared" ref="F10:F17" si="1">(E10*1000)/(D10*1000)</f>
+        <v>10.036203297520773</v>
+      </c>
+      <c r="G10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11">
+        <v>266540</v>
+      </c>
+      <c r="E11">
+        <v>2509187</v>
+      </c>
+      <c r="F11" s="5">
+        <f t="shared" si="1"/>
+        <v>9.4139228633600958</v>
+      </c>
+      <c r="G11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12">
+        <v>537321</v>
+      </c>
+      <c r="E12">
+        <v>5176493</v>
+      </c>
+      <c r="F12" s="5">
+        <f t="shared" si="1"/>
+        <v>9.6338929615630136</v>
+      </c>
+      <c r="G12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" t="s">
+        <v>154</v>
+      </c>
+      <c r="D13">
+        <v>25711</v>
+      </c>
+      <c r="E13">
+        <v>597528</v>
+      </c>
+      <c r="F13" s="5">
+        <f t="shared" si="1"/>
+        <v>23.240169577223757</v>
+      </c>
+      <c r="G13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D14">
+        <v>42391</v>
+      </c>
+      <c r="E14">
+        <v>717492</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="1"/>
+        <v>16.925573824632586</v>
+      </c>
+      <c r="G14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D15">
+        <v>62501</v>
+      </c>
+      <c r="E15">
+        <v>2547076</v>
+      </c>
+      <c r="F15" s="5">
+        <f t="shared" si="1"/>
+        <v>40.752563958976658</v>
+      </c>
+      <c r="G15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D16">
+        <v>10779</v>
+      </c>
+      <c r="E16">
+        <v>463669</v>
+      </c>
+      <c r="F16" s="5">
+        <f t="shared" si="1"/>
+        <v>43.015956953335191</v>
+      </c>
+      <c r="G16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D17">
+        <v>141381</v>
+      </c>
+      <c r="E17">
+        <v>4325765</v>
+      </c>
+      <c r="F17" s="5">
+        <f t="shared" si="1"/>
+        <v>30.596508724651827</v>
+      </c>
+      <c r="G17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18">
+        <v>18</v>
+      </c>
+      <c r="E18">
+        <v>1276</v>
+      </c>
+      <c r="F18" s="5">
+        <f t="shared" ref="F18:F22" si="2">(E18*1000)/D18</f>
+        <v>70888.888888888891</v>
+      </c>
+      <c r="G18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19">
+        <v>4941</v>
+      </c>
+      <c r="E19">
+        <v>287552</v>
+      </c>
+      <c r="F19" s="5">
+        <f t="shared" si="2"/>
+        <v>58197.12608783647</v>
+      </c>
+      <c r="G19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20">
+        <v>16549</v>
+      </c>
+      <c r="E20">
+        <v>1269872</v>
+      </c>
+      <c r="F20" s="5">
+        <f t="shared" si="2"/>
+        <v>76734.062481116678</v>
+      </c>
+      <c r="G20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21">
+        <v>153</v>
+      </c>
+      <c r="E21">
+        <v>10553</v>
+      </c>
+      <c r="F21" s="5">
+        <f t="shared" si="2"/>
+        <v>68973.856209150326</v>
+      </c>
+      <c r="G21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22">
+        <v>21660</v>
+      </c>
+      <c r="E22">
+        <v>1569254</v>
+      </c>
+      <c r="F22" s="5">
+        <f t="shared" si="2"/>
+        <v>72449.399815327793</v>
+      </c>
+      <c r="G22" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23">
+        <v>9515</v>
+      </c>
+      <c r="E23">
+        <v>1633456</v>
+      </c>
+      <c r="F23" s="6">
+        <f>(E23*1000)/(D23*1000000)</f>
+        <v>0.17167167630057803</v>
+      </c>
+      <c r="G23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{740C5C6D-65F6-485E-9AA5-45CED2729404}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/Prices/Prices_data.xlsx
+++ b/data/Prices/Prices_data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="458" documentId="13_ncr:9_{F62047AF-F3A2-4C22-8968-B3120DE95FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F97160AD-C6FC-4667-9F7F-97D34292217A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{EC527E92-74B5-47BF-A0A5-1376B6EBFE76}"/>
+    <workbookView xWindow="-28920" yWindow="-705" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{EC527E92-74B5-47BF-A0A5-1376B6EBFE76}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="2" r:id="rId1"/>
@@ -3239,7 +3239,7 @@
   <cols>
     <col min="1" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="8.81640625" customWidth="1"/>
     <col min="6" max="6" width="6.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.26953125" bestFit="1" customWidth="1"/>
